--- a/tests/fixtures/xlsx/test.xlsx
+++ b/tests/fixtures/xlsx/test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WangWenXuan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WangWenXuan\Documents\GitHub\latexsnipper-core\tests\fixtures\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69CAB257-70DD-42C9-A646-CC4BB4723460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6F1E06-C2FF-4914-BD45-18E08C13B8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2470" windowWidth="16800" windowHeight="9520" xr2:uid="{DD03BCFC-86B9-4F99-A019-BA765104C188}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{DD03BCFC-86B9-4F99-A019-BA765104C188}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -109,6 +109,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>150931</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0950D171-16B4-D3C5-733E-B7368A818F2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1339850" y="0"/>
+          <a:ext cx="4754681" cy="3397249"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -450,5 +499,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>